--- a/employee_surveys/021_employee_morale_survey--employee_surveys.xlsx
+++ b/employee_surveys/021_employee_morale_survey--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job</t>
+          <t>how_satisfied_with_your_job_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>How satisfied are you with your job</t>
+          <t>How Satisfied With Your Job 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>work_life_balance</t>
+          <t>work_life_balance_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Work-life balance</t>
+          <t>Work Life Balance 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>work_pressure</t>
+          <t>work_pressure_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Work pressure</t>
+          <t>Work Pressure 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>job_satisfaction</t>
+          <t>job_satisfaction_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Job satisfaction</t>
+          <t>Job Satisfaction 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1731,7 +1731,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job_choices</t>
+          <t>how_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job_choices</t>
+          <t>how_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job_choices</t>
+          <t>how_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job_choices</t>
+          <t>how_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>how_satisfied_with_your_job_choices</t>
+          <t>how_satisfied_with_your_job_2_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2088,7 +2088,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2105,7 +2105,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2122,7 +2122,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2156,7 +2156,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>work_life_balance_choices</t>
+          <t>work_life_balance_2_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2173,7 +2173,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>work_pressure_choices</t>
+          <t>work_pressure_2_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2190,7 +2190,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>work_pressure_choices</t>
+          <t>work_pressure_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2207,7 +2207,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>work_pressure_choices</t>
+          <t>work_pressure_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2224,7 +2224,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>work_pressure_choices</t>
+          <t>work_pressure_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2241,7 +2241,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2258,7 +2258,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2275,7 +2275,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -2292,7 +2292,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>job_satisfaction_choices</t>
+          <t>job_satisfaction_2_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
